--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96829</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128515649</v>
       </c>
       <c r="B2" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128515645</v>
       </c>
       <c r="B3" t="n">
-        <v>96892</v>
+        <v>96897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128515647</v>
       </c>
       <c r="B4" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,200 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130667805</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92476</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>632041</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6641951</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130667586</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97196</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>632106</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6642008</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92483</v>
+        <v>92496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>130667805</v>
       </c>
       <c r="B5" t="n">
-        <v>92498</v>
+        <v>92506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97220</v>
+        <v>97229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128515649</v>
+        <v>128515646</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632063</v>
+        <v>632036</v>
       </c>
       <c r="R2" t="n">
-        <v>6641946</v>
+        <v>6641943</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128515645</v>
+        <v>130667805</v>
       </c>
       <c r="B3" t="n">
-        <v>96897</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Fibysjön, Upl</t>
+          <t>Fiby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632105</v>
+        <v>632041</v>
       </c>
       <c r="R3" t="n">
-        <v>6642009</v>
+        <v>6641951</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sara Lundkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128515647</v>
+        <v>128515649</v>
       </c>
       <c r="B4" t="n">
-        <v>92218</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632056</v>
+        <v>632063</v>
       </c>
       <c r="R4" t="n">
-        <v>6641969</v>
+        <v>6641946</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,48 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130667805</v>
+        <v>128515645</v>
       </c>
       <c r="B5" t="n">
-        <v>92530</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fiby, Upl</t>
+          <t>Östra Fibysjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632041</v>
+        <v>632105</v>
       </c>
       <c r="R5" t="n">
-        <v>6641951</v>
+        <v>6642009</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>130667586</v>
       </c>
       <c r="B6" t="n">
-        <v>97253</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128515647</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Östra Fibysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>632056</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6641969</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,48 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128515646</v>
+        <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>92632</v>
+        <v>97565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Fibysjön, Upl</t>
+          <t>Fiby, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632036</v>
+        <v>632111</v>
       </c>
       <c r="R4" t="n">
-        <v>6641943</v>
+        <v>6642023</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +979,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128515646</t>
+          <t>https://artportalen.se/Sighting/136442750</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128515647</v>
+        <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>92632</v>
+        <v>97565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Fibysjön, Upl</t>
+          <t>Fiby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632056</v>
+        <v>632110</v>
       </c>
       <c r="R5" t="n">
-        <v>6641969</v>
+        <v>6642013</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,49 +1091,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128515647</t>
+          <t>https://artportalen.se/Sighting/136442752</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130667805</v>
+        <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>92632</v>
+        <v>97565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632041</v>
+        <v>632161</v>
       </c>
       <c r="R6" t="n">
-        <v>6641951</v>
+        <v>6642073</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1203,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Lundkvist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130667805</t>
+          <t>https://artportalen.se/Sighting/136442759</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128515649</v>
+        <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>96759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1231,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Fibysjön, Upl</t>
+          <t>Fiby, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632063</v>
+        <v>632058</v>
       </c>
       <c r="R7" t="n">
-        <v>6641946</v>
+        <v>6641979</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1285,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,18 +1315,1770 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136442747</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136442743</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92359</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>632039</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6641909</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442743</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136442739</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92088</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>632092</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6641889</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442739</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136442744</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92088</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>632050</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6641907</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442744</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136442751</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92088</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>632111</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6642014</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442751</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136442755</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92088</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>632088</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6641947</v>
+      </c>
+      <c r="S12" t="n">
+        <v>22</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442755</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136442760</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92088</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>632290</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6642173</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442760</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136442740</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92520</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>632071</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6641870</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442740</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136442754</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92520</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>632091</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6641944</v>
+      </c>
+      <c r="S15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442754</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136442748</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96663</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>632059</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6641971</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442748</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136442753</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96663</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>632108</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6641995</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442753</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128515646</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Östra Fibysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>632036</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6641943</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128515646</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128515647</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Östra Fibysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>632056</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6641969</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128515647</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130667805</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>632041</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6641951</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130667805</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136442746</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92313</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>632062</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6641965</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442746</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128515649</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Östra Fibysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>632063</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6641946</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128515649</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136442745</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101440</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fiby, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>632056</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6641948</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136442745</t>
         </is>
       </c>
     </row>
@@ -1298,6 +3090,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92313</v>
+        <v>92326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101440</v>
+        <v>101453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96676</v>
+        <v>96677</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92326</v>
+        <v>92327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
